--- a/banco/tb_centralizadora.xlsx
+++ b/banco/tb_centralizadora.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp_811_10-2022\htdocs\FNDE\banco\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mbs10065305\xampp_8_2\htdocs\fnde\banco\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="161">
   <si>
     <t>sigla_se</t>
   </si>
@@ -77,9 +77,6 @@
     <t>CLI BRASILIA</t>
   </si>
   <si>
-    <t>CTE BRASILIA</t>
-  </si>
-  <si>
     <t>CE</t>
   </si>
   <si>
@@ -290,9 +287,6 @@
     <t>CLI SOROCABA</t>
   </si>
   <si>
-    <t>FNDE_LIMEIRA</t>
-  </si>
-  <si>
     <t>SPM</t>
   </si>
   <si>
@@ -312,6 +306,207 @@
   </si>
   <si>
     <t>CLI PALMAS</t>
+  </si>
+  <si>
+    <t>sigla_centralizadora</t>
+  </si>
+  <si>
+    <t>RBO</t>
+  </si>
+  <si>
+    <t>MCO</t>
+  </si>
+  <si>
+    <t>MNS</t>
+  </si>
+  <si>
+    <t>MCP</t>
+  </si>
+  <si>
+    <t>FSA</t>
+  </si>
+  <si>
+    <t>JUA</t>
+  </si>
+  <si>
+    <t>SDR</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>FLA</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>VTA</t>
+  </si>
+  <si>
+    <t>GYN</t>
+  </si>
+  <si>
+    <t>ITZ</t>
+  </si>
+  <si>
+    <t>SIS</t>
+  </si>
+  <si>
+    <t>SLS</t>
+  </si>
+  <si>
+    <t>MOC</t>
+  </si>
+  <si>
+    <t>TAP</t>
+  </si>
+  <si>
+    <t>ULA</t>
+  </si>
+  <si>
+    <t>UNI</t>
+  </si>
+  <si>
+    <t>VGA</t>
+  </si>
+  <si>
+    <t>CVL</t>
+  </si>
+  <si>
+    <t>GVS</t>
+  </si>
+  <si>
+    <t>CBA</t>
+  </si>
+  <si>
+    <t>BLM</t>
+  </si>
+  <si>
+    <t>MAB</t>
+  </si>
+  <si>
+    <t>JPA</t>
+  </si>
+  <si>
+    <t>POS</t>
+  </si>
+  <si>
+    <t>CRU</t>
+  </si>
+  <si>
+    <t>RCE</t>
+  </si>
+  <si>
+    <t>SGP</t>
+  </si>
+  <si>
+    <t>TSA</t>
+  </si>
+  <si>
+    <t>CSC</t>
+  </si>
+  <si>
+    <t>LDA</t>
+  </si>
+  <si>
+    <t>PIN</t>
+  </si>
+  <si>
+    <t>PGO</t>
+  </si>
+  <si>
+    <t>BFC</t>
+  </si>
+  <si>
+    <t>CPS</t>
+  </si>
+  <si>
+    <t>NTL</t>
+  </si>
+  <si>
+    <t>JIP</t>
+  </si>
+  <si>
+    <t>BVA</t>
+  </si>
+  <si>
+    <t>PAS</t>
+  </si>
+  <si>
+    <t>PLT</t>
+  </si>
+  <si>
+    <t>PAE</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>SAN</t>
+  </si>
+  <si>
+    <t>NHO</t>
+  </si>
+  <si>
+    <t>BNU</t>
+  </si>
+  <si>
+    <t>CCO</t>
+  </si>
+  <si>
+    <t>FNS</t>
+  </si>
+  <si>
+    <t>CRT</t>
+  </si>
+  <si>
+    <t>AJU</t>
+  </si>
+  <si>
+    <t>BRU</t>
+  </si>
+  <si>
+    <t>CAS</t>
+  </si>
+  <si>
+    <t>PPE</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>SJO</t>
+  </si>
+  <si>
+    <t>SJC</t>
+  </si>
+  <si>
+    <t>SOC</t>
+  </si>
+  <si>
+    <t>LIM</t>
+  </si>
+  <si>
+    <t>FNDE LIMEIRA</t>
+  </si>
+  <si>
+    <t>GRS</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>SAM</t>
+  </si>
+  <si>
+    <t>VLP</t>
+  </si>
+  <si>
+    <t>PMW</t>
   </si>
 </sst>
 </file>
@@ -324,12 +519,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -344,8 +545,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,554 +829,748 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
+      <c r="C22" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>30</v>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="B24" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>30</v>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>38</v>
+    <row r="27" spans="1:3">
+      <c r="A27" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>40</v>
+    <row r="28" spans="1:3">
+      <c r="A28" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="B28" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>40</v>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>43</v>
+    <row r="30" spans="1:3">
+      <c r="A30" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="B30" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>43</v>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>46</v>
+    <row r="32" spans="1:3">
+      <c r="A32" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>46</v>
+      <c r="C32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="B33" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>46</v>
+      <c r="C33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>50</v>
+    <row r="35" spans="1:3">
+      <c r="A35" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>52</v>
+    <row r="36" spans="1:3">
+      <c r="A36" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>52</v>
+      <c r="C37" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="B38" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>52</v>
+      <c r="C38" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="B39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>57</v>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="B40" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>57</v>
+      <c r="C40" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="B41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>60</v>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>62</v>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="B43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>64</v>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="B44" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>66</v>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="B45" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>66</v>
+      <c r="C45" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="B46" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>66</v>
+      <c r="C46" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="B47" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>66</v>
+      <c r="C47" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="B48" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>66</v>
+      <c r="C48" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="B49" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>66</v>
+      <c r="C49" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="B50" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>73</v>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="B51" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>73</v>
+      <c r="C51" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="B52" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>73</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="C52" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>73</v>
+      <c r="C53" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="B54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>78</v>
+    <row r="55" spans="1:3">
+      <c r="A55" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="B55" t="s">
+        <v>80</v>
+      </c>
+      <c r="C55" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>80</v>
+    <row r="56" spans="1:3">
+      <c r="A56" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="B56" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>80</v>
+      <c r="C56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="B57" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>80</v>
+      <c r="C57" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="B58" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>80</v>
+      <c r="C58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="B59" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>80</v>
+      <c r="C59" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="B60" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>80</v>
+      <c r="C60" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="B61" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>80</v>
+      <c r="C61" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="B62" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>80</v>
+        <v>155</v>
+      </c>
+      <c r="C62" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="B63" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
+      <c r="C63" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" t="s">
         <v>89</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>89</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>159</v>
+      </c>
+      <c r="B66" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>89</v>
-      </c>
-      <c r="B66" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+      <c r="C66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="B67" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>94</v>
-      </c>
-      <c r="B68" t="s">
-        <v>95</v>
+      <c r="C67" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
